--- a/data/daily_age_gender/【2025年8月】デイリー年齢性別.xlsx
+++ b/data/daily_age_gender/【2025年8月】デイリー年齢性別.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -23,7 +23,7 @@
     <t>レポート終了日</t>
   </si>
   <si>
-    <t>広告セット名</t>
+    <t>キャンペーン名</t>
   </si>
   <si>
     <t>年齢</t>
@@ -32,7 +32,7 @@
     <t>性別</t>
   </si>
   <si>
-    <t>広告セットの配信</t>
+    <t>キャンペーンの配信</t>
   </si>
   <si>
     <t>アトリビューション設定</t>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>終了日時</t>
-  </si>
-  <si>
-    <t>開始</t>
   </si>
   <si>
     <t>インプレッション</t>
@@ -456,10 +453,10 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="20" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,13 +538,10 @@
       <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:28">
-      <c r="A2" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
